--- a/work/base-diaria/BASE DIÁRIA/Base Ranking diário_DF7d.xlsx
+++ b/work/base-diaria/BASE DIÁRIA/Base Ranking diário_DF7d.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t> </t>
   </si>
@@ -72,7 +72,7 @@
     <t>Calculation Date/Time</t>
   </si>
   <si>
-    <t>09/07/2026 13:00:19</t>
+    <t>10/07/2026 13:00:39</t>
   </si>
   <si>
     <t>Reference target (IND)</t>
@@ -90,7 +90,7 @@
     <t>Datas</t>
   </si>
   <si>
-    <t>10/06/2026, 17/06/2026, 24/06/2026, 01/07/2026</t>
+    <t>11/06/2026, 18/06/2026, 25/06/2026, 02/07/2026</t>
   </si>
   <si>
     <t>Targets</t>
@@ -195,123 +195,114 @@
     <t>JORNAL NACIONAL SS</t>
   </si>
   <si>
+    <t>DF TV 2A EDICAO SS</t>
+  </si>
+  <si>
+    <t>NOVELA II SS</t>
+  </si>
+  <si>
     <t>NOVELA III SS</t>
   </si>
   <si>
+    <t>NOVELA I SS</t>
+  </si>
+  <si>
+    <t>COPA DO MUNDO NOT</t>
+  </si>
+  <si>
     <t>COPA DO MUNDO VES</t>
   </si>
   <si>
-    <t>DF TV 2A EDICAO SS</t>
-  </si>
-  <si>
-    <t>NOVELA II SS</t>
-  </si>
-  <si>
-    <t>NOVELA I SS</t>
+    <t>CENTRAL DA COPA NOT</t>
+  </si>
+  <si>
+    <t>JORNAL HOJE</t>
+  </si>
+  <si>
+    <t>GLOBO ESPORTE</t>
+  </si>
+  <si>
+    <t>DF TV 1A EDICAO</t>
+  </si>
+  <si>
+    <t>CINEMA ESPECIAL NOT 1</t>
   </si>
   <si>
     <t>NOVELA IV</t>
   </si>
   <si>
-    <t>GLOBO ESPORTE</t>
-  </si>
-  <si>
-    <t>DF TV 1A EDICAO</t>
-  </si>
-  <si>
-    <t>JORNAL HOJE</t>
-  </si>
-  <si>
-    <t>ANOS 90 EXPL PAGODE</t>
-  </si>
-  <si>
-    <t>COPA DO MUNDO NOT</t>
-  </si>
-  <si>
-    <t>BOL DF TV</t>
+    <t>BOM DIA DF</t>
+  </si>
+  <si>
+    <t>NOVELA ED ESPECIAL</t>
+  </si>
+  <si>
+    <t>BOM DIA BRASIL</t>
   </si>
   <si>
     <t>VALE A PENA VER DE NOVO</t>
   </si>
   <si>
-    <t>NOVELA ED ESPECIAL</t>
-  </si>
-  <si>
-    <t>BOM DIA BRASIL</t>
-  </si>
-  <si>
-    <t>SESSAO DA TARDE</t>
-  </si>
-  <si>
-    <t>BOM DIA DF</t>
+    <t>MAIS VOCE</t>
   </si>
   <si>
     <t>ENCONTRO</t>
   </si>
   <si>
-    <t>MAIS VOCE</t>
-  </si>
-  <si>
     <t>CENTRAL DA COPA MAD</t>
   </si>
   <si>
-    <t>VAI BRASIL</t>
-  </si>
-  <si>
-    <t>CONTAGEM REGRESSIVA</t>
+    <t>JORNAL DA GLOBO</t>
+  </si>
+  <si>
+    <t>REAPRES NOVELA MAD</t>
   </si>
   <si>
     <t>HORA UM</t>
   </si>
   <si>
-    <t>CENTRAL DA COPA NOT</t>
-  </si>
-  <si>
-    <t>JORNAL DA GLOBO</t>
-  </si>
-  <si>
-    <t>REAPRES NOVELA MAD</t>
-  </si>
-  <si>
     <t>REAPRES NOVELA</t>
   </si>
   <si>
+    <t>CORUJAO</t>
+  </si>
+  <si>
+    <t>COPA DO MUNDO MAD</t>
+  </si>
+  <si>
     <t>SESSAO COMED MADRUG</t>
   </si>
   <si>
-    <t>CORUJAO</t>
-  </si>
-  <si>
     <t>Record (Total Domicílios|Distrito Federal|Live)</t>
   </si>
   <si>
     <t>Record TV</t>
   </si>
   <si>
+    <t>JORNAL DA RECORD</t>
+  </si>
+  <si>
+    <t>DF RECORD</t>
+  </si>
+  <si>
+    <t>NOVELA 3</t>
+  </si>
+  <si>
     <t>CIDADE ALERTA DF</t>
   </si>
   <si>
-    <t>DF RECORD</t>
-  </si>
-  <si>
-    <t>JORNAL DA RECORD</t>
+    <t>NOVELA 22H</t>
+  </si>
+  <si>
+    <t>BALANCO GERAL DFE</t>
   </si>
   <si>
     <t>RELIGIOSO VES</t>
   </si>
   <si>
-    <t>NOVELA 3</t>
-  </si>
-  <si>
-    <t>BALANCO GERAL DFE</t>
-  </si>
-  <si>
     <t>CIDADE ALERTA</t>
   </si>
   <si>
-    <t>NOVELA 22H</t>
-  </si>
-  <si>
     <t>NOVELA DA TARDE 1</t>
   </si>
   <si>
@@ -321,223 +312,223 @@
     <t>CASA DO PATRAO</t>
   </si>
   <si>
+    <t>HOJE EM DIA</t>
+  </si>
+  <si>
     <t>FALA BRASIL</t>
   </si>
   <si>
-    <t>HOJE EM DIA</t>
-  </si>
-  <si>
     <t>SERIE PREMIUM</t>
   </si>
   <si>
     <t>DF NO AR</t>
   </si>
   <si>
-    <t>CINE RECORD ESPECIAL</t>
-  </si>
-  <si>
     <t>JR 24H MAD</t>
   </si>
   <si>
+    <t>FALA QUE EU TE ESCUTO MAD</t>
+  </si>
+  <si>
+    <t>INTELIGENCIA E FE MAD</t>
+  </si>
+  <si>
+    <t>RELIGIOSO MAD</t>
+  </si>
+  <si>
     <t>JR 24H MAT</t>
   </si>
   <si>
     <t>RELIGIOSO MAT</t>
   </si>
   <si>
-    <t>ESCOLA DO AMOR MAD</t>
-  </si>
-  <si>
-    <t>FALA QUE EU TE ESCUTO MAD</t>
-  </si>
-  <si>
-    <t>RELIGIOSO MAD</t>
-  </si>
-  <si>
     <t>SBT (Total Domicílios|Distrito Federal|Live)</t>
   </si>
   <si>
+    <t>NOVELA NOITE 2</t>
+  </si>
+  <si>
+    <t>SBT BRASIL</t>
+  </si>
+  <si>
+    <t>AQUI AGORA NOT</t>
+  </si>
+  <si>
+    <t>PROGRAMA DO RATINHO</t>
+  </si>
+  <si>
+    <t>SBT BRASILIA 2 ED</t>
+  </si>
+  <si>
+    <t>NOVELA NOITE 18H</t>
+  </si>
+  <si>
     <t>VEM PRO JOGO NOT</t>
   </si>
   <si>
-    <t>NOVELA NOITE 2</t>
-  </si>
-  <si>
-    <t>SBT BRASIL</t>
-  </si>
-  <si>
-    <t>NOVELA NOITE 1</t>
-  </si>
-  <si>
-    <t>NOVELA NOITE 18H</t>
-  </si>
-  <si>
-    <t>PROGRAMA DO RATINHO</t>
-  </si>
-  <si>
     <t>NOVELA TARDE 14H</t>
   </si>
   <si>
-    <t>AQUI AGORA NOT</t>
+    <t>SERIE VESPERTINA</t>
+  </si>
+  <si>
+    <t>A PRACA E NOSSA NOT</t>
+  </si>
+  <si>
+    <t>SBT BRASILIA 1 ED</t>
+  </si>
+  <si>
+    <t>FOFOCALIZANDO</t>
+  </si>
+  <si>
+    <t>SBT SPORTS BRASILIA</t>
+  </si>
+  <si>
+    <t>VEM PRO JOGO VES</t>
+  </si>
+  <si>
+    <t>BALANCO DA COPA</t>
+  </si>
+  <si>
+    <t>THE NOITE</t>
+  </si>
+  <si>
+    <t>PRIMEIRO IMPACTO</t>
+  </si>
+  <si>
+    <t>SBT NOTICIAS MAD</t>
+  </si>
+  <si>
+    <t>OPERACAO MESQUITA</t>
+  </si>
+  <si>
+    <t>SE LIGA BRASIL LOCAL</t>
+  </si>
+  <si>
+    <t>SE LIGA BRASIL</t>
+  </si>
+  <si>
+    <t>BAND (Total Domicílios|Distrito Federal|Live)</t>
+  </si>
+  <si>
+    <t>BOA TARDE DF</t>
+  </si>
+  <si>
+    <t>JORNAL DA BAND</t>
+  </si>
+  <si>
+    <t>JOGO ABERTO MAT</t>
+  </si>
+  <si>
+    <t>BAND CIDADE DFE NOT</t>
+  </si>
+  <si>
+    <t>OS DONOS DA BOLA</t>
+  </si>
+  <si>
+    <t>BRASIL URGENTE DF</t>
+  </si>
+  <si>
+    <t>MELHOR DA TARDE</t>
+  </si>
+  <si>
+    <t>BRASIL URGENTE 1</t>
+  </si>
+  <si>
+    <t>JORNAL DA NOITE</t>
+  </si>
+  <si>
+    <t>NOVELA II NOT</t>
+  </si>
+  <si>
+    <t>ESPORTE TOTAL MAD</t>
+  </si>
+  <si>
+    <t>BORA BRASIL</t>
+  </si>
+  <si>
+    <t>BANDSPORTS NEWS</t>
+  </si>
+  <si>
+    <t>NOVELA III</t>
+  </si>
+  <si>
+    <t>LINHA DE COMBATE NOT</t>
+  </si>
+  <si>
+    <t>RELIGIOSO NOT</t>
+  </si>
+  <si>
+    <t>AGRO BAND MAT</t>
+  </si>
+  <si>
+    <t>RedeTv (Total Domicílios|Distrito Federal|Live)</t>
+  </si>
+  <si>
+    <t>TV FAMA</t>
+  </si>
+  <si>
+    <t>A TARDE E SUA</t>
+  </si>
+  <si>
+    <t>RAPIDINHAS DA FAMA</t>
+  </si>
+  <si>
+    <t>DF ALERTA</t>
   </si>
   <si>
     <t>INTERPROGRAMA</t>
   </si>
   <si>
-    <t>SBT BRASILIA 2 ED</t>
-  </si>
-  <si>
-    <t>TORCIDA SBT VES</t>
-  </si>
-  <si>
-    <t>VEM PRO JOGO VES</t>
-  </si>
-  <si>
-    <t>FABRICA DE CASAMENTOS</t>
-  </si>
-  <si>
-    <t>SERIE VESPERTINA</t>
-  </si>
-  <si>
-    <t>FOFOCALIZANDO</t>
-  </si>
-  <si>
-    <t>SBT SPORTS BRASILIA</t>
-  </si>
-  <si>
-    <t>SBT BRASILIA 1 ED</t>
-  </si>
-  <si>
-    <t>PASSE DE MILHOES</t>
-  </si>
-  <si>
-    <t>BALANCO DA COPA</t>
-  </si>
-  <si>
-    <t>THE NOITE</t>
-  </si>
-  <si>
-    <t>SE LIGA BRASIL</t>
-  </si>
-  <si>
-    <t>PRIMEIRO IMPACTO</t>
-  </si>
-  <si>
-    <t>OPERACAO MESQUITA</t>
-  </si>
-  <si>
-    <t>SE LIGA BRASIL LOCAL</t>
-  </si>
-  <si>
-    <t>SBT NOTICIAS MAD</t>
-  </si>
-  <si>
-    <t>BAND (Total Domicílios|Distrito Federal|Live)</t>
-  </si>
-  <si>
-    <t>JOGO ABERTO MAT</t>
-  </si>
-  <si>
-    <t>BAND CIDADE DFE NOT</t>
-  </si>
-  <si>
-    <t>JORNAL DA BAND</t>
-  </si>
-  <si>
-    <t>JORNAL DA NOITE</t>
-  </si>
-  <si>
-    <t>CINE CLUBE</t>
-  </si>
-  <si>
-    <t>BOA TARDE DF</t>
-  </si>
-  <si>
-    <t>BRASIL URGENTE 1</t>
-  </si>
-  <si>
-    <t>ESPORTE TOTAL MAD</t>
-  </si>
-  <si>
-    <t>MELHOR DA TARDE</t>
-  </si>
-  <si>
-    <t>BRASIL URGENTE DF</t>
-  </si>
-  <si>
-    <t>OS DONOS DA BOLA</t>
-  </si>
-  <si>
-    <t>BORA BRASIL</t>
-  </si>
-  <si>
-    <t>NOVELA II NOT</t>
-  </si>
-  <si>
-    <t>BANDSPORTS NEWS</t>
-  </si>
-  <si>
-    <t>RELIGIOSO NOT</t>
-  </si>
-  <si>
-    <t>AGRO BAND MAT</t>
-  </si>
-  <si>
-    <t>RedeTv (Total Domicílios|Distrito Federal|Live)</t>
-  </si>
-  <si>
-    <t>TV FAMA</t>
-  </si>
-  <si>
-    <t>A TARDE E SUA</t>
-  </si>
-  <si>
-    <t>SUPERPOP</t>
+    <t>OPERACAO DE RISCO NOT 2</t>
+  </si>
+  <si>
+    <t>LEITURA DINAMICA SSX</t>
+  </si>
+  <si>
+    <t>A HORA DO ZAP VES 1</t>
+  </si>
+  <si>
+    <t>HIPER XCAP</t>
+  </si>
+  <si>
+    <t>VITRINE TV BRASIL VES</t>
+  </si>
+  <si>
+    <t>REDE TV NOTICIAS 1A ED</t>
+  </si>
+  <si>
+    <t>REDE TV NEWS</t>
+  </si>
+  <si>
+    <t>CB PONTO PODER VES 1</t>
+  </si>
+  <si>
+    <t>CB PONTO SAUDE</t>
+  </si>
+  <si>
+    <t>BRASIL DO POVO</t>
+  </si>
+  <si>
+    <t>CB PONTO SAUDE MAD</t>
   </si>
   <si>
     <t>JORNAL LOCAL 2A EDICAO</t>
   </si>
   <si>
-    <t>RAPIDINHAS DA FAMA</t>
-  </si>
-  <si>
-    <t>DF ALERTA</t>
-  </si>
-  <si>
-    <t>BRASIL DO POVO</t>
-  </si>
-  <si>
-    <t>REDE TV NEWS</t>
-  </si>
-  <si>
-    <t>LEITURA DINAMICA SSX</t>
-  </si>
-  <si>
-    <t>A HORA DO ZAP VES 1</t>
-  </si>
-  <si>
-    <t>REDE TV NOTICIAS 1A ED</t>
+    <t>FICA COM A GENTE</t>
+  </si>
+  <si>
+    <t>JORNAL LOCAL 2A EDICAO MAD</t>
   </si>
   <si>
     <t>A HORA DO ZAP MAD</t>
   </si>
   <si>
-    <t>FICA COM A GENTE</t>
-  </si>
-  <si>
-    <t>CB PONTO PODER VES</t>
-  </si>
-  <si>
     <t>BOLA NA REDE MAT</t>
   </si>
   <si>
     <t>CB PONTO PODER MAD</t>
-  </si>
-  <si>
-    <t>JORNAL LOCAL 2A EDICAO MAD</t>
-  </si>
-  <si>
-    <t>VITRINE TV BRASIL VES</t>
   </si>
 </sst>
 </file>
@@ -1354,10 +1345,10 @@
         <v>57</v>
       </c>
       <c r="C4" s="4">
-        <v>20.74</v>
+        <v>21.58</v>
       </c>
       <c r="D4" s="4">
-        <v>35.63</v>
+        <v>36.81</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1368,10 +1359,10 @@
         <v>58</v>
       </c>
       <c r="C5" s="4">
-        <v>19.76</v>
+        <v>20.86</v>
       </c>
       <c r="D5" s="4">
-        <v>35.94</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1382,10 +1373,10 @@
         <v>59</v>
       </c>
       <c r="C6" s="4">
-        <v>19.72</v>
+        <v>19.59</v>
       </c>
       <c r="D6" s="4">
-        <v>37.04</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1396,10 +1387,10 @@
         <v>60</v>
       </c>
       <c r="C7" s="4">
-        <v>19.08</v>
+        <v>18.84</v>
       </c>
       <c r="D7" s="4">
-        <v>34.79</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1410,10 +1401,10 @@
         <v>61</v>
       </c>
       <c r="C8" s="4">
-        <v>18.64</v>
+        <v>16.30</v>
       </c>
       <c r="D8" s="4">
-        <v>32.65</v>
+        <v>34.37</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1424,10 +1415,10 @@
         <v>62</v>
       </c>
       <c r="C9" s="4">
-        <v>15.24</v>
+        <v>13.83</v>
       </c>
       <c r="D9" s="4">
-        <v>28.51</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1438,10 +1429,10 @@
         <v>63</v>
       </c>
       <c r="C10" s="4">
-        <v>12.82</v>
+        <v>13.47</v>
       </c>
       <c r="D10" s="4">
-        <v>28.43</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1452,10 +1443,10 @@
         <v>64</v>
       </c>
       <c r="C11" s="4">
-        <v>12.76</v>
+        <v>13.31</v>
       </c>
       <c r="D11" s="4">
-        <v>34.45</v>
+        <v>28.58</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1466,10 +1457,10 @@
         <v>65</v>
       </c>
       <c r="C12" s="4">
-        <v>12.16</v>
+        <v>13.17</v>
       </c>
       <c r="D12" s="4">
-        <v>37.22</v>
+        <v>32.43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1480,10 +1471,10 @@
         <v>66</v>
       </c>
       <c r="C13" s="4">
-        <v>11.37</v>
+        <v>12.96</v>
       </c>
       <c r="D13" s="4">
-        <v>30.19</v>
+        <v>32.70</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1494,10 +1485,10 @@
         <v>67</v>
       </c>
       <c r="C14" s="4">
-        <v>10.28</v>
+        <v>12.18</v>
       </c>
       <c r="D14" s="4">
-        <v>24.65</v>
+        <v>33.56</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1508,10 +1499,10 @@
         <v>68</v>
       </c>
       <c r="C15" s="4">
-        <v>10.17</v>
+        <v>11.24</v>
       </c>
       <c r="D15" s="4">
-        <v>28.51</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1522,10 +1513,10 @@
         <v>69</v>
       </c>
       <c r="C16" s="4">
-        <v>8.90</v>
+        <v>8.64</v>
       </c>
       <c r="D16" s="4">
-        <v>23.32</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1536,10 +1527,10 @@
         <v>70</v>
       </c>
       <c r="C17" s="4">
-        <v>7.95</v>
+        <v>8.42</v>
       </c>
       <c r="D17" s="4">
-        <v>22.12</v>
+        <v>58.64</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1550,10 +1541,10 @@
         <v>71</v>
       </c>
       <c r="C18" s="4">
-        <v>7.65</v>
+        <v>8.31</v>
       </c>
       <c r="D18" s="4">
-        <v>21.63</v>
+        <v>22.40</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1564,10 +1555,10 @@
         <v>72</v>
       </c>
       <c r="C19" s="4">
-        <v>7.62</v>
+        <v>8.12</v>
       </c>
       <c r="D19" s="4">
-        <v>44.96</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1578,10 +1569,10 @@
         <v>73</v>
       </c>
       <c r="C20" s="4">
-        <v>7.36</v>
+        <v>8.12</v>
       </c>
       <c r="D20" s="4">
-        <v>21.18</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1592,10 +1583,10 @@
         <v>74</v>
       </c>
       <c r="C21" s="4">
-        <v>6.95</v>
+        <v>7.63</v>
       </c>
       <c r="D21" s="4">
-        <v>56.28</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1606,10 +1597,10 @@
         <v>75</v>
       </c>
       <c r="C22" s="4">
-        <v>6.12</v>
+        <v>7.07</v>
       </c>
       <c r="D22" s="4">
-        <v>31.53</v>
+        <v>32.11</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1620,10 +1611,10 @@
         <v>76</v>
       </c>
       <c r="C23" s="4">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="D23" s="4">
-        <v>26.74</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1634,10 +1625,10 @@
         <v>77</v>
       </c>
       <c r="C24" s="4">
-        <v>5.85</v>
+        <v>4.32</v>
       </c>
       <c r="D24" s="4">
-        <v>31.37</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1648,10 +1639,10 @@
         <v>78</v>
       </c>
       <c r="C25" s="4">
-        <v>5.41</v>
+        <v>3.59</v>
       </c>
       <c r="D25" s="4">
-        <v>20.62</v>
+        <v>23.31</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1662,10 +1653,10 @@
         <v>79</v>
       </c>
       <c r="C26" s="4">
-        <v>4.50</v>
+        <v>3.47</v>
       </c>
       <c r="D26" s="4">
-        <v>25.45</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1676,10 +1667,10 @@
         <v>80</v>
       </c>
       <c r="C27" s="4">
-        <v>4.14</v>
+        <v>2.95</v>
       </c>
       <c r="D27" s="4">
-        <v>53.18</v>
+        <v>26.90</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1690,10 +1681,10 @@
         <v>81</v>
       </c>
       <c r="C28" s="4">
-        <v>4.01</v>
+        <v>2.66</v>
       </c>
       <c r="D28" s="4">
-        <v>14.57</v>
+        <v>30.64</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1704,10 +1695,10 @@
         <v>82</v>
       </c>
       <c r="C29" s="4">
-        <v>3.79</v>
+        <v>2.38</v>
       </c>
       <c r="D29" s="4">
-        <v>23.98</v>
+        <v>23.76</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1718,52 +1709,10 @@
         <v>83</v>
       </c>
       <c r="C30" s="4">
-        <v>3.19</v>
+        <v>1.82</v>
       </c>
       <c r="D30" s="4">
-        <v>30.95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="B31" t="s" s="3">
-        <v>84</v>
-      </c>
-      <c r="C31" s="4">
-        <v>2.90</v>
-      </c>
-      <c r="D31" s="4">
-        <v>26.40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="B32" t="s" s="3">
-        <v>85</v>
-      </c>
-      <c r="C32" s="4">
-        <v>2.41</v>
-      </c>
-      <c r="D32" s="4">
-        <v>26.97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="B33" t="s" s="3">
-        <v>86</v>
-      </c>
-      <c r="C33" s="4">
-        <v>1.89</v>
-      </c>
-      <c r="D33" s="4">
-        <v>25.94</v>
+        <v>25.58</v>
       </c>
     </row>
   </sheetData>
@@ -1781,7 +1730,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1812,310 +1761,296 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C4" s="4">
-        <v>4.95</v>
+        <v>5.90</v>
       </c>
       <c r="D4" s="4">
-        <v>9.81</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4">
-        <v>4.84</v>
+        <v>5.04</v>
       </c>
       <c r="D5" s="4">
-        <v>8.83</v>
+        <v>8.89</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s" s="3">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s" s="3">
         <v>88</v>
       </c>
-      <c r="B6" t="s" s="3">
-        <v>91</v>
-      </c>
       <c r="C6" s="4">
-        <v>4.59</v>
+        <v>4.98</v>
       </c>
       <c r="D6" s="4">
-        <v>7.95</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" s="4">
-        <v>3.97</v>
+        <v>4.36</v>
       </c>
       <c r="D7" s="4">
-        <v>10.74</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" s="4">
-        <v>3.90</v>
+        <v>4.00</v>
       </c>
       <c r="D8" s="4">
-        <v>6.73</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" s="4">
-        <v>3.72</v>
+        <v>3.89</v>
       </c>
       <c r="D9" s="4">
-        <v>10.66</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" s="4">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="D10" s="4">
-        <v>8.35</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C11" s="4">
-        <v>3.24</v>
+        <v>2.83</v>
       </c>
       <c r="D11" s="4">
-        <v>6.26</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" s="4">
-        <v>2.83</v>
+        <v>2.58</v>
       </c>
       <c r="D12" s="4">
-        <v>8.43</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C13" s="4">
-        <v>2.81</v>
+        <v>2.56</v>
       </c>
       <c r="D13" s="4">
-        <v>7.46</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C14" s="4">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="D14" s="4">
-        <v>6.01</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15" s="4">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="D15" s="4">
-        <v>11.93</v>
+        <v>8.80</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C16" s="4">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="D16" s="4">
-        <v>9.10</v>
+        <v>8.39</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C17" s="4">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="D17" s="4">
-        <v>4.04</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C18" s="4">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="D18" s="4">
-        <v>7.30</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C19" s="4">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="D19" s="4">
-        <v>1.18</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C20" s="4">
-        <v>0.57</v>
+        <v>0.60</v>
       </c>
       <c r="D20" s="4">
-        <v>2.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C21" s="4">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="D21" s="4">
-        <v>2.63</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C22" s="4">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="D22" s="4">
-        <v>2.11</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C23" s="4">
-        <v>0.18</v>
+        <v>0.09</v>
       </c>
       <c r="D23" s="4">
-        <v>1.92</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C24" s="4">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="D24" s="4">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s" s="3">
-        <v>88</v>
-      </c>
-      <c r="B25" t="s" s="3">
-        <v>110</v>
-      </c>
-      <c r="C25" s="4">
-        <v>0.08</v>
-      </c>
-      <c r="D25" s="4">
-        <v>1.03</v>
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -2133,7 +2068,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2167,13 +2102,13 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4">
-        <v>12.33</v>
+        <v>3.83</v>
       </c>
       <c r="D4" s="4">
-        <v>16.91</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2181,13 +2116,13 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4">
-        <v>4.80</v>
+        <v>3.81</v>
       </c>
       <c r="D5" s="4">
-        <v>8.63</v>
+        <v>6.60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2195,13 +2130,13 @@
         <v>30</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4">
-        <v>4.06</v>
+        <v>3.78</v>
       </c>
       <c r="D6" s="4">
-        <v>7.24</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2209,13 +2144,13 @@
         <v>30</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4">
-        <v>3.93</v>
+        <v>3.39</v>
       </c>
       <c r="D7" s="4">
-        <v>6.74</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2223,13 +2158,13 @@
         <v>30</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4">
-        <v>3.62</v>
+        <v>3.36</v>
       </c>
       <c r="D8" s="4">
-        <v>6.39</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2237,13 +2172,13 @@
         <v>30</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="C9" s="4">
-        <v>3.39</v>
+        <v>3.33</v>
       </c>
       <c r="D9" s="4">
-        <v>7.87</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2251,13 +2186,13 @@
         <v>30</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10" s="4">
-        <v>3.11</v>
+        <v>2.90</v>
       </c>
       <c r="D10" s="4">
-        <v>6.46</v>
+        <v>4.90</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2265,13 +2200,13 @@
         <v>30</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C11" s="4">
-        <v>3.11</v>
+        <v>2.86</v>
       </c>
       <c r="D11" s="4">
-        <v>7.06</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2279,13 +2214,13 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4">
-        <v>2.91</v>
+        <v>2.81</v>
       </c>
       <c r="D12" s="4">
-        <v>7.90</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2293,13 +2228,13 @@
         <v>30</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C13" s="4">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="D13" s="4">
-        <v>5.46</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2307,13 +2242,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4">
-        <v>2.66</v>
+        <v>2.19</v>
       </c>
       <c r="D14" s="4">
-        <v>4.87</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2321,13 +2256,13 @@
         <v>30</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C15" s="4">
-        <v>2.39</v>
+        <v>2.05</v>
       </c>
       <c r="D15" s="4">
-        <v>4.34</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2335,13 +2270,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C16" s="4">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="D16" s="4">
-        <v>5.69</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2349,13 +2284,13 @@
         <v>30</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C17" s="4">
-        <v>2.07</v>
+        <v>1.79</v>
       </c>
       <c r="D17" s="4">
-        <v>5.79</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2363,13 +2298,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C18" s="4">
-        <v>1.93</v>
+        <v>1.49</v>
       </c>
       <c r="D18" s="4">
-        <v>6.15</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2377,13 +2312,13 @@
         <v>30</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C19" s="4">
-        <v>1.90</v>
+        <v>1.47</v>
       </c>
       <c r="D19" s="4">
-        <v>4.99</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2391,13 +2326,13 @@
         <v>30</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C20" s="4">
-        <v>1.65</v>
+        <v>1.18</v>
       </c>
       <c r="D20" s="4">
-        <v>4.82</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2405,13 +2340,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C21" s="4">
-        <v>1.46</v>
+        <v>0.63</v>
       </c>
       <c r="D21" s="4">
-        <v>4.08</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2419,13 +2354,13 @@
         <v>30</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C22" s="4">
-        <v>1.46</v>
+        <v>0.59</v>
       </c>
       <c r="D22" s="4">
-        <v>5.32</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2433,13 +2368,13 @@
         <v>30</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C23" s="4">
-        <v>0.92</v>
+        <v>0.50</v>
       </c>
       <c r="D23" s="4">
-        <v>10.66</v>
+        <v>5.84</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2447,13 +2382,13 @@
         <v>30</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C24" s="4">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="D24" s="4">
-        <v>3.35</v>
+        <v>4.00</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2461,13 +2396,13 @@
         <v>30</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C25" s="4">
-        <v>0.75</v>
+        <v>0.42</v>
       </c>
       <c r="D25" s="4">
-        <v>4.84</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2475,69 +2410,13 @@
         <v>30</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C26" s="4">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="D26" s="4">
-        <v>7.09</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>133</v>
-      </c>
-      <c r="C27" s="4">
-        <v>0.68</v>
-      </c>
-      <c r="D27" s="4">
-        <v>3.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="B28" t="s" s="3">
-        <v>134</v>
-      </c>
-      <c r="C28" s="4">
-        <v>0.62</v>
-      </c>
-      <c r="D28" s="4">
-        <v>5.93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="B29" t="s" s="3">
-        <v>135</v>
-      </c>
-      <c r="C29" s="4">
-        <v>0.61</v>
-      </c>
-      <c r="D29" s="4">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="B30" t="s" s="3">
-        <v>136</v>
-      </c>
-      <c r="C30" s="4">
-        <v>0.38</v>
-      </c>
-      <c r="D30" s="4">
-        <v>4.87</v>
+        <v>3.11</v>
       </c>
     </row>
   </sheetData>
@@ -2555,7 +2434,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>137</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2589,13 +2468,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4">
-        <v>0.53</v>
+        <v>1.24</v>
       </c>
       <c r="D4" s="4">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2603,13 +2482,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C5" s="4">
-        <v>0.52</v>
+        <v>1.16</v>
       </c>
       <c r="D5" s="4">
-        <v>0.87</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2617,13 +2496,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C6" s="4">
-        <v>0.48</v>
+        <v>0.86</v>
       </c>
       <c r="D6" s="4">
-        <v>0.78</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2631,13 +2510,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="C7" s="4">
-        <v>0.40</v>
+        <v>0.80</v>
       </c>
       <c r="D7" s="4">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2645,13 +2524,13 @@
         <v>32</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C8" s="4">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="D8" s="4">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2659,13 +2538,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C9" s="4">
-        <v>0.37</v>
+        <v>0.53</v>
       </c>
       <c r="D9" s="4">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2673,13 +2552,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C10" s="4">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="D10" s="4">
-        <v>0.96</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2687,13 +2566,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C11" s="4">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="D11" s="4">
-        <v>2.50</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2701,13 +2580,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C12" s="4">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="D12" s="4">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2715,13 +2594,13 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="C13" s="4">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="D13" s="4">
-        <v>0.44</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2729,13 +2608,13 @@
         <v>32</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C14" s="4">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="D14" s="4">
-        <v>0.52</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2743,13 +2622,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4">
-        <v>0.09</v>
+        <v>0.10</v>
       </c>
       <c r="D15" s="4">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2757,13 +2636,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4">
         <v>0.08</v>
       </c>
       <c r="D16" s="4">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2771,10 +2650,10 @@
         <v>32</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C17" s="4">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="D17" s="4">
         <v>0.12</v>
@@ -2785,13 +2664,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4">
-        <v>0.07</v>
+        <v>0.02</v>
       </c>
       <c r="D18" s="4">
-        <v>0.83</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2799,13 +2678,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C19" s="4">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D19" s="4">
-        <v>0.37</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2813,13 +2692,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="C20" s="4">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D20" s="4">
-        <v>0.08</v>
+        <v>0.10</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2827,13 +2706,13 @@
         <v>32</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C21" s="4">
-        <v>0.01</v>
+        <v>0.00</v>
       </c>
       <c r="D21" s="4">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2841,13 +2720,13 @@
         <v>32</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C22" s="4">
-        <v>0.01</v>
+        <v>0.00</v>
       </c>
       <c r="D22" s="4">
-        <v>0.08</v>
+        <v>0.00</v>
       </c>
     </row>
   </sheetData>
@@ -2865,7 +2744,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2899,13 +2778,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C4" s="4">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="D4" s="4">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2913,13 +2792,13 @@
         <v>31</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4">
-        <v>0.57</v>
+        <v>0.82</v>
       </c>
       <c r="D5" s="4">
-        <v>1.64</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2927,13 +2806,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4">
-        <v>0.39</v>
+        <v>0.67</v>
       </c>
       <c r="D6" s="4">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2941,13 +2820,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C7" s="4">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="D7" s="4">
-        <v>0.53</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2955,13 +2834,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="D8" s="4">
-        <v>0.67</v>
+        <v>0.50</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2969,13 +2848,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C9" s="4">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="D9" s="4">
-        <v>0.44</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2983,13 +2862,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C10" s="4">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="D10" s="4">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2997,13 +2876,13 @@
         <v>31</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>92</v>
+        <v>154</v>
       </c>
       <c r="C11" s="4">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="D11" s="4">
-        <v>0.41</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3011,13 +2890,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C12" s="4">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="D12" s="4">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3025,13 +2904,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C13" s="4">
         <v>0.14</v>
       </c>
       <c r="D13" s="4">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3039,13 +2918,13 @@
         <v>31</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="D14" s="4">
-        <v>0.40</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3053,13 +2932,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C15" s="4">
-        <v>0.07</v>
+        <v>0.12</v>
       </c>
       <c r="D15" s="4">
-        <v>0.20</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3067,13 +2946,13 @@
         <v>31</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="D16" s="4">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3081,13 +2960,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C17" s="4">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="D17" s="4">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3095,13 +2974,13 @@
         <v>31</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="D18" s="4">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3109,13 +2988,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="C19" s="4">
-        <v>0.02</v>
+        <v>0.10</v>
       </c>
       <c r="D19" s="4">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3123,13 +3002,13 @@
         <v>31</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4">
-        <v>0.02</v>
+        <v>0.10</v>
       </c>
       <c r="D20" s="4">
-        <v>0.08</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3137,13 +3016,13 @@
         <v>31</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C21" s="4">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="D21" s="4">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3151,13 +3030,13 @@
         <v>31</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="C22" s="4">
-        <v>0.01</v>
+        <v>0.07</v>
       </c>
       <c r="D22" s="4">
-        <v>0.06</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3165,13 +3044,13 @@
         <v>31</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="C23" s="4">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="D23" s="4">
-        <v>0.10</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3179,13 +3058,13 @@
         <v>31</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C24" s="4">
-        <v>0.00</v>
+        <v>0.06</v>
       </c>
       <c r="D24" s="4">
-        <v>0.00</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3193,13 +3072,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C25" s="4">
-        <v>0.00</v>
+        <v>0.04</v>
       </c>
       <c r="D25" s="4">
-        <v>0.00</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3207,12 +3086,54 @@
         <v>31</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C26" s="4">
+        <v>0.04</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s" s="3">
+        <v>168</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0.01</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s" s="3">
+        <v>106</v>
+      </c>
+      <c r="C28" s="4">
         <v>0.00</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D28" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="B29" t="s" s="3">
+        <v>169</v>
+      </c>
+      <c r="C29" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="D29" s="4">
         <v>0.00</v>
       </c>
     </row>
